--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include ValueSet #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:48:16+00:00</t>
+    <t>2026-02-23T18:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,25 +100,13 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-encounter-participant</t>
-  </si>
-  <si>
     <t>ValueSet URL</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j387-role-participant-ms</t>
   </si>
 </sst>
 </file>
@@ -382,7 +370,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -397,22 +385,6 @@
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -431,12 +403,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T18:02:53+00:00</t>
+    <t>2026-02-24T08:32:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T08:32:52+00:00</t>
+    <t>2026-02-26T16:12:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include ValueSet #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:12:14+00:00</t>
+    <t>2026-02-27T13:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -104,9 +103,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j387-role-participant-ms</t>
   </si>
 </sst>
 </file>
@@ -390,28 +386,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T13:39:19+00:00</t>
+    <t>2026-02-27T14:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T14:39:40+00:00</t>
+    <t>2026-02-27T15:25:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/ValueSet-tddui-encounter-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T15:25:53+00:00</t>
+    <t>2026-02-27T15:59:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
